--- a/Week-01/Ex4B_more_GTrends.xlsx
+++ b/Week-01/Ex4B_more_GTrends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lilywells\Documents\DataAnalytics\Week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156A0026-73FD-4FEE-B2FE-A1B69BDFD4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D2E857-17CD-4F17-9345-61CC892CBB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{54973A18-4CE6-43F8-8661-100CBE931653}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="By Search Term" sheetId="1" r:id="rId1"/>
     <sheet name="By State" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Search Term'!$A$1:$E$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1509,6 +1512,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{92EFB794-76FA-4ECC-8586-29E18793D806}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
